--- a/01_Business_Understanding/Risk_Matrix.xlsx
+++ b/01_Business_Understanding/Risk_Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta-my.sharepoint.com/personal/umgz4a_psoplaneta_com/Documents/DATA/Analytics Projects/Product_Analytics/01_Business_Understanding/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="14_{508BBB18-27FD-432E-8AE1-2D355900285E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB850BCA-A7B7-4656-A5FA-6C0E72DC3ECF}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="14_{508BBB18-27FD-432E-8AE1-2D355900285E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A13E868-2D1D-45F1-8AD2-BFA11DFE1C45}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F3905514-F28A-4C51-ACE5-B8311BBBF468}"/>
   </bookViews>
@@ -399,10 +399,6 @@
 - Repositorios completos con toda la documentación por fase</t>
   </si>
   <si>
-    <t xml:space="preserve"> -Notificar al resto de integrantes a penas se active el riesgo
-  -Confirmar con el Director Financiero el nuevo responsible o stakeholder</t>
-  </si>
-  <si>
     <t>Deficiencia de Perfiles</t>
   </si>
   <si>
@@ -762,13 +758,17 @@
   </si>
   <si>
     <t xml:space="preserve"> -Solicitudes formales y seguimiento mediante correos de solicitud</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -Notificar al resto de integrantes a penas se active el riesgo
+  -Confirmar con el Director Producto el nuevo responsible o stakeholder</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1580,13 +1580,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F990E2-5129-ED4D-BF55-72114F3AE8A2}">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="15.453125" customWidth="1"/>
     <col min="11" max="11" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12">
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="F1" s="38"/>
       <c r="G1" s="38"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12">
       <c r="A2" s="38"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -1606,8 +1606,8 @@
       <c r="F2" s="38"/>
       <c r="G2" s="38"/>
     </row>
-    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="15" thickBot="1"/>
+    <row r="4" spans="1:12" ht="30" customHeight="1" thickBot="1">
       <c r="A4" s="35" t="s">
         <v>1</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="15" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>4</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="29.15" customHeight="1">
       <c r="A6" s="19">
         <v>1</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="29.15" customHeight="1">
       <c r="A7" s="19">
         <v>2</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="15" thickBot="1">
       <c r="A8" s="19">
         <v>3</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12">
       <c r="A9" s="19">
         <v>4</v>
       </c>
@@ -1723,7 +1723,7 @@
       <c r="F9" s="31"/>
       <c r="G9" s="32"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12">
       <c r="A10" s="19">
         <v>5</v>
       </c>
@@ -1739,7 +1739,7 @@
       <c r="G10" s="32"/>
       <c r="K10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12">
       <c r="A11" s="19">
         <v>6</v>
       </c>
@@ -1755,7 +1755,7 @@
       <c r="G11" s="32"/>
       <c r="K11" s="6"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12">
       <c r="A12" s="19">
         <v>7</v>
       </c>
@@ -1771,7 +1771,7 @@
       <c r="G12" s="32"/>
       <c r="K12" s="6"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12">
       <c r="A13" s="19">
         <v>8</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="F13" s="31"/>
       <c r="G13" s="32"/>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="15" thickBot="1">
       <c r="A14" s="20" t="s">
         <v>29</v>
       </c>
@@ -1801,11 +1801,11 @@
       <c r="F14" s="29"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="15" thickBot="1">
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="29.15" customHeight="1">
       <c r="A16" s="35" t="s">
         <v>32</v>
       </c>
@@ -1816,7 +1816,7 @@
       <c r="F16" s="36"/>
       <c r="G16" s="37"/>
     </row>
-    <row r="17" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="16" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>4</v>
       </c>
@@ -1831,7 +1831,7 @@
       <c r="F17" s="33"/>
       <c r="G17" s="34"/>
     </row>
-    <row r="18" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="16" customHeight="1">
       <c r="A18" s="19">
         <v>1</v>
       </c>
@@ -1846,7 +1846,7 @@
       <c r="F18" s="31"/>
       <c r="G18" s="32"/>
     </row>
-    <row r="19" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" ht="16" customHeight="1">
       <c r="A19" s="19">
         <v>2</v>
       </c>
@@ -1861,7 +1861,7 @@
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
     </row>
-    <row r="20" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="16" customHeight="1">
       <c r="A20" s="19">
         <v>3</v>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="F20" s="31"/>
       <c r="G20" s="32"/>
     </row>
-    <row r="21" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="16" customHeight="1">
       <c r="A21" s="19">
         <v>4</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="F21" s="31"/>
       <c r="G21" s="32"/>
     </row>
-    <row r="22" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="16" customHeight="1">
       <c r="A22" s="19">
         <v>5</v>
       </c>
@@ -1906,7 +1906,7 @@
       <c r="F22" s="31"/>
       <c r="G22" s="32"/>
     </row>
-    <row r="23" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="16" customHeight="1">
       <c r="A23" s="19">
         <v>6</v>
       </c>
@@ -1923,7 +1923,7 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="16" customHeight="1">
       <c r="A24" s="19">
         <v>7</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="F24" s="31"/>
       <c r="G24" s="32"/>
     </row>
-    <row r="25" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="16" customHeight="1">
       <c r="A25" s="19">
         <v>8</v>
       </c>
@@ -1953,7 +1953,7 @@
       <c r="F25" s="31"/>
       <c r="G25" s="32"/>
     </row>
-    <row r="26" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="16" customHeight="1">
       <c r="A26" s="19">
         <v>9</v>
       </c>
@@ -1968,7 +1968,7 @@
       <c r="F26" s="31"/>
       <c r="G26" s="32"/>
     </row>
-    <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" ht="15" thickBot="1">
       <c r="A27" s="20">
         <v>10</v>
       </c>
@@ -1983,8 +1983,8 @@
       <c r="F27" s="29"/>
       <c r="G27" s="30"/>
     </row>
-    <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="29" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="15" thickBot="1"/>
+    <row r="29" spans="1:14" ht="28" customHeight="1">
       <c r="A29" s="35" t="s">
         <v>47</v>
       </c>
@@ -1998,7 +1998,7 @@
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14">
       <c r="A30" s="18" t="s">
         <v>4</v>
       </c>
@@ -2013,7 +2013,7 @@
       <c r="F30" s="33"/>
       <c r="G30" s="34"/>
     </row>
-    <row r="31" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="16" customHeight="1">
       <c r="A31" s="19">
         <v>1</v>
       </c>
@@ -2028,7 +2028,7 @@
       <c r="F31" s="31"/>
       <c r="G31" s="32"/>
     </row>
-    <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="16" customHeight="1">
       <c r="A32" s="19">
         <v>2</v>
       </c>
@@ -2043,7 +2043,7 @@
       <c r="F32" s="31"/>
       <c r="G32" s="32"/>
     </row>
-    <row r="33" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="16" customHeight="1">
       <c r="A33" s="19">
         <v>3</v>
       </c>
@@ -2058,7 +2058,7 @@
       <c r="F33" s="31"/>
       <c r="G33" s="32"/>
     </row>
-    <row r="34" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="16" customHeight="1">
       <c r="A34" s="19">
         <v>4</v>
       </c>
@@ -2073,7 +2073,7 @@
       <c r="F34" s="31"/>
       <c r="G34" s="32"/>
     </row>
-    <row r="35" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="16" customHeight="1">
       <c r="A35" s="19">
         <v>5</v>
       </c>
@@ -2088,7 +2088,7 @@
       <c r="F35" s="31"/>
       <c r="G35" s="32"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7">
       <c r="A36" s="19">
         <v>6</v>
       </c>
@@ -2103,7 +2103,7 @@
       <c r="F36" s="31"/>
       <c r="G36" s="32"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7">
       <c r="A37" s="19">
         <v>7</v>
       </c>
@@ -2118,7 +2118,7 @@
       <c r="F37" s="31"/>
       <c r="G37" s="32"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7">
       <c r="A38" s="19">
         <v>8</v>
       </c>
@@ -2133,7 +2133,7 @@
       <c r="F38" s="31"/>
       <c r="G38" s="32"/>
     </row>
-    <row r="39" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="16" customHeight="1">
       <c r="A39" s="19">
         <v>9</v>
       </c>
@@ -2148,7 +2148,7 @@
       <c r="F39" s="31"/>
       <c r="G39" s="32"/>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="15" thickBot="1">
       <c r="A40" s="20">
         <v>10</v>
       </c>
@@ -2241,7 +2241,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981DFF4C-D7B8-4B9A-9E6D-BE2F2A02BC59}">
   <dimension ref="A2:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="48.453125" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" customWidth="1"/>
@@ -2255,13 +2255,13 @@
     <col min="12" max="12" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="55.5" customHeight="1">
       <c r="A2" s="21" t="s">
         <v>69</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="25"/>
@@ -2270,14 +2270,14 @@
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I2" s="27"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
       <c r="L2" s="28"/>
     </row>
-    <row r="4" spans="1:12" ht="51.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="51.65" customHeight="1">
       <c r="A4" s="15" t="s">
         <v>71</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="34.5">
       <c r="A5" s="12" t="s">
         <v>83</v>
       </c>
@@ -2351,10 +2351,10 @@
         <v>89</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="57.5" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="57.5">
       <c r="A6" s="12" t="s">
         <v>83</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="46">
       <c r="A7" s="12" t="s">
         <v>83</v>
       </c>
@@ -2429,10 +2429,10 @@
         <v>102</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="34.5">
       <c r="A8" s="12" t="s">
         <v>83</v>
       </c>
@@ -2465,13 +2465,13 @@
         <v>200</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34.5">
       <c r="A9" s="12" t="s">
         <v>83</v>
       </c>
@@ -2507,10 +2507,10 @@
         <v>111</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="69" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="69">
       <c r="A10" s="12" t="s">
         <v>112</v>
       </c>
@@ -2543,36 +2543,36 @@
         <v>60</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="46">
       <c r="A11" s="12" t="s">
         <v>112</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="E11" s="14">
         <v>9</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G11" s="14">
         <v>2</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I11" s="14">
         <v>3</v>
@@ -2582,36 +2582,36 @@
         <v>54</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="34.5">
       <c r="A12" s="12" t="s">
         <v>112</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D12" s="13" t="s">
         <v>126</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>127</v>
       </c>
       <c r="E12" s="14">
         <v>3</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G12" s="14">
         <v>2</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I12" s="14">
         <v>2</v>
@@ -2621,36 +2621,36 @@
         <v>12</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="34.5">
       <c r="A13" s="12" t="s">
         <v>112</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="E13" s="14">
         <v>7</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G13" s="14">
         <v>7</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I13" s="14">
         <v>2</v>
@@ -2663,33 +2663,33 @@
         <v>111</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="47.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="47.15" customHeight="1">
       <c r="A14" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>139</v>
       </c>
       <c r="E14" s="14">
         <v>9</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G14" s="14">
         <v>6</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
@@ -2699,36 +2699,36 @@
         <v>108</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="46">
       <c r="A15" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>145</v>
       </c>
       <c r="E15" s="14">
         <v>7</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -2738,30 +2738,30 @@
         <v>245</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="46">
       <c r="A16" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>152</v>
       </c>
       <c r="E16" s="14">
         <v>9</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G16" s="14">
         <v>4</v>
@@ -2777,36 +2777,36 @@
         <v>144</v>
       </c>
       <c r="K16" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="34.5">
+      <c r="A17" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="E17" s="14">
         <v>10</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G17" s="14">
         <v>6</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I17" s="14">
         <v>3</v>
@@ -2816,36 +2816,36 @@
         <v>180</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="34.5">
       <c r="A18" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="D18" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>162</v>
       </c>
       <c r="E18" s="14">
         <v>10</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G18" s="14">
         <v>9</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I18" s="14">
         <v>5</v>
@@ -2855,36 +2855,36 @@
         <v>450</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="46">
       <c r="A19" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B19" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D19" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>168</v>
       </c>
       <c r="E19" s="14">
         <v>6</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G19" s="14">
         <v>8</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I19" s="14">
         <v>3</v>
@@ -2894,36 +2894,36 @@
         <v>144</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="46">
       <c r="A20" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>174</v>
       </c>
       <c r="E20" s="14">
         <v>7</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G20" s="14">
         <v>6</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
@@ -2933,36 +2933,36 @@
         <v>252</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="46">
       <c r="A21" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B21" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
         <v>179</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>180</v>
       </c>
       <c r="E21" s="14">
         <v>7</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G21" s="14">
         <v>5</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I21" s="14">
         <v>4</v>
@@ -2972,30 +2972,30 @@
         <v>140</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="34.5">
       <c r="A22" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C22" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>184</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>185</v>
       </c>
       <c r="E22" s="14">
         <v>7</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G22" s="14">
         <v>7</v>
@@ -3011,36 +3011,36 @@
         <v>196</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="46">
       <c r="A23" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>187</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>188</v>
       </c>
       <c r="E23" s="14">
         <v>9</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G23" s="14">
         <v>6</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I23" s="14">
         <v>6</v>
@@ -3050,36 +3050,36 @@
         <v>324</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="23">
       <c r="A24" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>192</v>
       </c>
       <c r="E24" s="14">
         <v>5</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G24" s="14">
         <v>7</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I24" s="14">
         <v>2</v>
@@ -3089,36 +3089,36 @@
         <v>70</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="46">
       <c r="A25" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
         <v>198</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>199</v>
       </c>
       <c r="E25" s="14">
         <v>10</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G25" s="14">
         <v>4</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I25" s="14">
         <v>3</v>
@@ -3128,36 +3128,36 @@
         <v>120</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L25" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="57.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="46">
       <c r="A26" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="D26" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E26" s="14">
         <v>8</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G26" s="14">
         <v>6</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I26" s="14">
         <v>5</v>
@@ -3167,36 +3167,36 @@
         <v>240</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="46">
       <c r="A27" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="D27" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E27" s="14">
         <v>9</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G27" s="14">
         <v>7</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -3206,36 +3206,36 @@
         <v>315</v>
       </c>
       <c r="K27" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="46">
+      <c r="A28" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="46" x14ac:dyDescent="0.35">
-      <c r="A28" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="D28" s="13" t="s">
         <v>209</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>210</v>
       </c>
       <c r="E28" s="14">
         <v>9</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I28" s="14">
         <v>3</v>
@@ -3245,36 +3245,36 @@
         <v>189</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L28" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="34.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="34.5">
       <c r="A29" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="E29" s="14">
         <v>7</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G29" s="14">
         <v>8</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -3284,36 +3284,36 @@
         <v>112</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="46">
       <c r="A30" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>213</v>
-      </c>
       <c r="C30" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="E30" s="14">
         <v>3</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G30" s="14">
         <v>8</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -3323,36 +3323,36 @@
         <v>48</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="46" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="46">
       <c r="A31" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>226</v>
       </c>
       <c r="E31" s="14">
         <v>7</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G31" s="14">
         <v>5</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -3362,36 +3362,36 @@
         <v>105</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="23">
       <c r="A32" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C32" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>230</v>
       </c>
       <c r="E32" s="14">
         <v>4</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G32" s="14">
         <v>6</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I32" s="14">
         <v>4</v>
@@ -3401,7 +3401,7 @@
         <v>96</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L32" s="13" t="s">
         <v>95</v>
@@ -3443,6 +3443,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009200D15403517347BFCC7BEE816B18F5" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="0c32dd1c78c32883e2be75803a5ce93a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="299da364-5bd6-4856-b54f-296f95f3dc71" xmlns:ns3="b593fc4c-2af5-4cc2-b6db-90e9851bf100" xmlns:ns4="7fe59f34-55a4-4ccc-9a2c-36cfcecf2037" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26f70861ee05eb5a0a686bed56820165" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="299da364-5bd6-4856-b54f-296f95f3dc71"/>
@@ -3652,22 +3661,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D176CA-D60D-4C6B-9357-B515981BD982}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE5C243D-74E5-4C90-A7EA-1858FEC01C32}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3687,19 +3695,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BDD062B-0168-4311-840A-28E541099443}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1D176CA-D60D-4C6B-9357-B515981BD982}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>